--- a/order_forms/049_restaurant_sanitization_audit_order_form--order_forms.xlsx
+++ b/order_forms/049_restaurant_sanitization_audit_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,20 +525,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>restaurant sanitization audit order form</t>
+          <t>Restaurant Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,20 +548,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>restaurant sanitization audit order form</t>
+          <t>Date of Last Inspection</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,151 +571,151 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>restaurant sanitization audit order form</t>
+          <t>Is the restaurant currently open?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>restaurant_sanitization_audit_order_form_page_4</t>
+          <t>kitchen_cleanliness</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>restaurant sanitization audit order form</t>
+          <t>Is the kitchen clean and organized?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>restaurant_sanitization_audit_order_form_page_5</t>
+          <t>kitchen_temperature</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>restaurant sanitization audit order form</t>
+          <t>What is the current temperature of the kitchen?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>restaurant_sanitization_audit_order_form_page_6</t>
+          <t>last_water_test_date</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>restaurant sanitization audit order form</t>
+          <t>When was the last time the restaurant's water was tested?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>restaurant_sanitization_audit_order_form_page_7</t>
+          <t>sanitization</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>restaurant sanitization audit order form</t>
+          <t>Is the restaurant's dishwashing station properly sanitized?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>restaurant_sanitization_audit_order_form_page_8</t>
+          <t>equipment_cleaning_date</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>restaurant sanitization audit order form</t>
+          <t>What is the current date of the last time the restaurant's equipment was cleaned?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>restaurant_sanitization_audit_order_form_page_9</t>
+          <t>waste_disposal_area_cleanliness</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>restaurant sanitization audit order form</t>
+          <t>Is the restaurant's waste disposal area clean and well-maintained?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -758,7 +758,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>restaurant_sanitization_audit_order_form_page_1_choices</t>
+          <t>restaurant_sanitization_audit_order_form_page_3_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -775,7 +775,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>restaurant_sanitization_audit_order_form_page_1_choices</t>
+          <t>restaurant_sanitization_audit_order_form_page_3_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -792,7 +792,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>restaurant_sanitization_audit_order_form_page_6_choices</t>
+          <t>kitchen_cleanliness_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -809,7 +809,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>restaurant_sanitization_audit_order_form_page_6_choices</t>
+          <t>kitchen_cleanliness_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -826,7 +826,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>restaurant_sanitization_audit_order_form_page_9_choices</t>
+          <t>sanitization_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -843,7 +843,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>restaurant_sanitization_audit_order_form_page_9_choices</t>
+          <t>sanitization_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -852,6 +852,40 @@
         </is>
       </c>
       <c r="C7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>waste_disposal_area_cleanliness_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>waste_disposal_area_cleanliness_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
